--- a/proyectos_diseno/BASES_DE_DATOS/Adicionales.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Adicionales.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T22:44:31</t>
+          <t>2026-09-29T09:26:57</t>
         </is>
       </c>
     </row>
